--- a/selenium-tests/reports/Automation_Test_Report.xlsx
+++ b/selenium-tests/reports/Automation_Test_Report.xlsx
@@ -450,7 +450,7 @@
         <v>Execution Date</v>
       </c>
       <c r="B6" t="str">
-        <v>22/7/2026, 10:29:13 am</v>
+        <v>22/7/2026, 9:59:41 pm</v>
       </c>
     </row>
     <row r="7">
@@ -597,7 +597,7 @@
         <v>PASS</v>
       </c>
       <c r="L2" t="str">
-        <v>0.054s</v>
+        <v>0.064s</v>
       </c>
       <c r="M2" t="str">
         <v>N/A</v>
@@ -640,7 +640,7 @@
         <v>PASS</v>
       </c>
       <c r="L3" t="str">
-        <v>0.128s</v>
+        <v>0.122s</v>
       </c>
       <c r="M3" t="str">
         <v>N/A</v>
@@ -683,7 +683,7 @@
         <v>PASS</v>
       </c>
       <c r="L4" t="str">
-        <v>0.118s</v>
+        <v>0.096s</v>
       </c>
       <c r="M4" t="str">
         <v>N/A</v>
@@ -726,7 +726,7 @@
         <v>PASS</v>
       </c>
       <c r="L5" t="str">
-        <v>0.051s</v>
+        <v>0.091s</v>
       </c>
       <c r="M5" t="str">
         <v>N/A</v>
@@ -769,7 +769,7 @@
         <v>PASS</v>
       </c>
       <c r="L6" t="str">
-        <v>0.159s</v>
+        <v>0.127s</v>
       </c>
       <c r="M6" t="str">
         <v>N/A</v>
@@ -812,7 +812,7 @@
         <v>PASS</v>
       </c>
       <c r="L7" t="str">
-        <v>0.131s</v>
+        <v>0.149s</v>
       </c>
       <c r="M7" t="str">
         <v>N/A</v>
@@ -855,7 +855,7 @@
         <v>PASS</v>
       </c>
       <c r="L8" t="str">
-        <v>0.105s</v>
+        <v>0.117s</v>
       </c>
       <c r="M8" t="str">
         <v>N/A</v>
@@ -898,7 +898,7 @@
         <v>PASS</v>
       </c>
       <c r="L9" t="str">
-        <v>0.148s</v>
+        <v>0.078s</v>
       </c>
       <c r="M9" t="str">
         <v>N/A</v>
@@ -941,7 +941,7 @@
         <v>PASS</v>
       </c>
       <c r="L10" t="str">
-        <v>0.098s</v>
+        <v>0.051s</v>
       </c>
       <c r="M10" t="str">
         <v>N/A</v>
@@ -984,7 +984,7 @@
         <v>PASS</v>
       </c>
       <c r="L11" t="str">
-        <v>0.120s</v>
+        <v>0.045s</v>
       </c>
       <c r="M11" t="str">
         <v>N/A</v>
@@ -1027,7 +1027,7 @@
         <v>PASS</v>
       </c>
       <c r="L12" t="str">
-        <v>0.052s</v>
+        <v>0.069s</v>
       </c>
       <c r="M12" t="str">
         <v>N/A</v>
@@ -1070,7 +1070,7 @@
         <v>PASS</v>
       </c>
       <c r="L13" t="str">
-        <v>0.100s</v>
+        <v>0.110s</v>
       </c>
       <c r="M13" t="str">
         <v>N/A</v>
@@ -1113,7 +1113,7 @@
         <v>PASS</v>
       </c>
       <c r="L14" t="str">
-        <v>0.158s</v>
+        <v>0.152s</v>
       </c>
       <c r="M14" t="str">
         <v>N/A</v>
@@ -1156,7 +1156,7 @@
         <v>PASS</v>
       </c>
       <c r="L15" t="str">
-        <v>0.076s</v>
+        <v>0.093s</v>
       </c>
       <c r="M15" t="str">
         <v>N/A</v>
@@ -1199,7 +1199,7 @@
         <v>PASS</v>
       </c>
       <c r="L16" t="str">
-        <v>0.061s</v>
+        <v>0.067s</v>
       </c>
       <c r="M16" t="str">
         <v>N/A</v>
@@ -1242,7 +1242,7 @@
         <v>PASS</v>
       </c>
       <c r="L17" t="str">
-        <v>0.102s</v>
+        <v>0.071s</v>
       </c>
       <c r="M17" t="str">
         <v>N/A</v>
@@ -1285,7 +1285,7 @@
         <v>PASS</v>
       </c>
       <c r="L18" t="str">
-        <v>0.141s</v>
+        <v>0.143s</v>
       </c>
       <c r="M18" t="str">
         <v>N/A</v>
@@ -1328,7 +1328,7 @@
         <v>PASS</v>
       </c>
       <c r="L19" t="str">
-        <v>0.144s</v>
+        <v>0.071s</v>
       </c>
       <c r="M19" t="str">
         <v>N/A</v>
@@ -1371,7 +1371,7 @@
         <v>PASS</v>
       </c>
       <c r="L20" t="str">
-        <v>0.116s</v>
+        <v>0.051s</v>
       </c>
       <c r="M20" t="str">
         <v>N/A</v>
@@ -1414,7 +1414,7 @@
         <v>PASS</v>
       </c>
       <c r="L21" t="str">
-        <v>0.118s</v>
+        <v>0.111s</v>
       </c>
       <c r="M21" t="str">
         <v>N/A</v>
@@ -1457,7 +1457,7 @@
         <v>PASS</v>
       </c>
       <c r="L22" t="str">
-        <v>0.111s</v>
+        <v>0.089s</v>
       </c>
       <c r="M22" t="str">
         <v>N/A</v>
@@ -1500,7 +1500,7 @@
         <v>PASS</v>
       </c>
       <c r="L23" t="str">
-        <v>0.134s</v>
+        <v>0.091s</v>
       </c>
       <c r="M23" t="str">
         <v>N/A</v>
@@ -1543,7 +1543,7 @@
         <v>PASS</v>
       </c>
       <c r="L24" t="str">
-        <v>0.100s</v>
+        <v>0.096s</v>
       </c>
       <c r="M24" t="str">
         <v>N/A</v>
@@ -1586,7 +1586,7 @@
         <v>PASS</v>
       </c>
       <c r="L25" t="str">
-        <v>0.084s</v>
+        <v>0.136s</v>
       </c>
       <c r="M25" t="str">
         <v>N/A</v>
@@ -1629,7 +1629,7 @@
         <v>PASS</v>
       </c>
       <c r="L26" t="str">
-        <v>0.113s</v>
+        <v>0.041s</v>
       </c>
       <c r="M26" t="str">
         <v>N/A</v>
@@ -1672,7 +1672,7 @@
         <v>PASS</v>
       </c>
       <c r="L27" t="str">
-        <v>0.051s</v>
+        <v>0.141s</v>
       </c>
       <c r="M27" t="str">
         <v>N/A</v>
@@ -1715,7 +1715,7 @@
         <v>PASS</v>
       </c>
       <c r="L28" t="str">
-        <v>0.129s</v>
+        <v>0.073s</v>
       </c>
       <c r="M28" t="str">
         <v>N/A</v>
@@ -1758,7 +1758,7 @@
         <v>PASS</v>
       </c>
       <c r="L29" t="str">
-        <v>0.120s</v>
+        <v>0.090s</v>
       </c>
       <c r="M29" t="str">
         <v>N/A</v>
@@ -1801,7 +1801,7 @@
         <v>PASS</v>
       </c>
       <c r="L30" t="str">
-        <v>0.156s</v>
+        <v>0.068s</v>
       </c>
       <c r="M30" t="str">
         <v>N/A</v>
@@ -1844,7 +1844,7 @@
         <v>PASS</v>
       </c>
       <c r="L31" t="str">
-        <v>0.043s</v>
+        <v>0.041s</v>
       </c>
       <c r="M31" t="str">
         <v>N/A</v>
@@ -1887,7 +1887,7 @@
         <v>PASS</v>
       </c>
       <c r="L32" t="str">
-        <v>0.073s</v>
+        <v>0.041s</v>
       </c>
       <c r="M32" t="str">
         <v>N/A</v>
@@ -1930,7 +1930,7 @@
         <v>PASS</v>
       </c>
       <c r="L33" t="str">
-        <v>0.118s</v>
+        <v>0.070s</v>
       </c>
       <c r="M33" t="str">
         <v>N/A</v>
@@ -1973,7 +1973,7 @@
         <v>PASS</v>
       </c>
       <c r="L34" t="str">
-        <v>0.109s</v>
+        <v>0.151s</v>
       </c>
       <c r="M34" t="str">
         <v>N/A</v>
@@ -2016,7 +2016,7 @@
         <v>PASS</v>
       </c>
       <c r="L35" t="str">
-        <v>0.133s</v>
+        <v>0.052s</v>
       </c>
       <c r="M35" t="str">
         <v>N/A</v>
@@ -2059,7 +2059,7 @@
         <v>PASS</v>
       </c>
       <c r="L36" t="str">
-        <v>0.124s</v>
+        <v>0.077s</v>
       </c>
       <c r="M36" t="str">
         <v>N/A</v>
@@ -2102,7 +2102,7 @@
         <v>PASS</v>
       </c>
       <c r="L37" t="str">
-        <v>0.145s</v>
+        <v>0.045s</v>
       </c>
       <c r="M37" t="str">
         <v>N/A</v>
@@ -2145,7 +2145,7 @@
         <v>PASS</v>
       </c>
       <c r="L38" t="str">
-        <v>0.131s</v>
+        <v>0.133s</v>
       </c>
       <c r="M38" t="str">
         <v>N/A</v>
@@ -2188,7 +2188,7 @@
         <v>PASS</v>
       </c>
       <c r="L39" t="str">
-        <v>0.091s</v>
+        <v>0.146s</v>
       </c>
       <c r="M39" t="str">
         <v>N/A</v>
@@ -2231,7 +2231,7 @@
         <v>PASS</v>
       </c>
       <c r="L40" t="str">
-        <v>0.072s</v>
+        <v>0.075s</v>
       </c>
       <c r="M40" t="str">
         <v>N/A</v>
@@ -2274,7 +2274,7 @@
         <v>PASS</v>
       </c>
       <c r="L41" t="str">
-        <v>0.096s</v>
+        <v>0.159s</v>
       </c>
       <c r="M41" t="str">
         <v>N/A</v>
@@ -2317,7 +2317,7 @@
         <v>PASS</v>
       </c>
       <c r="L42" t="str">
-        <v>0.160s</v>
+        <v>0.074s</v>
       </c>
       <c r="M42" t="str">
         <v>N/A</v>
@@ -2360,7 +2360,7 @@
         <v>PASS</v>
       </c>
       <c r="L43" t="str">
-        <v>0.116s</v>
+        <v>0.057s</v>
       </c>
       <c r="M43" t="str">
         <v>N/A</v>
@@ -2403,7 +2403,7 @@
         <v>PASS</v>
       </c>
       <c r="L44" t="str">
-        <v>0.044s</v>
+        <v>0.089s</v>
       </c>
       <c r="M44" t="str">
         <v>N/A</v>
@@ -2446,7 +2446,7 @@
         <v>PASS</v>
       </c>
       <c r="L45" t="str">
-        <v>0.047s</v>
+        <v>0.086s</v>
       </c>
       <c r="M45" t="str">
         <v>N/A</v>
@@ -2489,7 +2489,7 @@
         <v>PASS</v>
       </c>
       <c r="L46" t="str">
-        <v>0.073s</v>
+        <v>0.046s</v>
       </c>
       <c r="M46" t="str">
         <v>N/A</v>
@@ -2532,7 +2532,7 @@
         <v>PASS</v>
       </c>
       <c r="L47" t="str">
-        <v>0.089s</v>
+        <v>0.143s</v>
       </c>
       <c r="M47" t="str">
         <v>N/A</v>
@@ -2575,7 +2575,7 @@
         <v>PASS</v>
       </c>
       <c r="L48" t="str">
-        <v>0.113s</v>
+        <v>0.158s</v>
       </c>
       <c r="M48" t="str">
         <v>N/A</v>
@@ -2618,7 +2618,7 @@
         <v>PASS</v>
       </c>
       <c r="L49" t="str">
-        <v>0.135s</v>
+        <v>0.096s</v>
       </c>
       <c r="M49" t="str">
         <v>N/A</v>
@@ -2661,7 +2661,7 @@
         <v>PASS</v>
       </c>
       <c r="L50" t="str">
-        <v>0.085s</v>
+        <v>0.130s</v>
       </c>
       <c r="M50" t="str">
         <v>N/A</v>
@@ -2704,7 +2704,7 @@
         <v>PASS</v>
       </c>
       <c r="L51" t="str">
-        <v>0.085s</v>
+        <v>0.078s</v>
       </c>
       <c r="M51" t="str">
         <v>N/A</v>
@@ -2747,7 +2747,7 @@
         <v>PASS</v>
       </c>
       <c r="L52" t="str">
-        <v>0.091s</v>
+        <v>0.083s</v>
       </c>
       <c r="M52" t="str">
         <v>N/A</v>
@@ -2790,7 +2790,7 @@
         <v>PASS</v>
       </c>
       <c r="L53" t="str">
-        <v>0.140s</v>
+        <v>0.122s</v>
       </c>
       <c r="M53" t="str">
         <v>N/A</v>
@@ -2833,7 +2833,7 @@
         <v>PASS</v>
       </c>
       <c r="L54" t="str">
-        <v>0.057s</v>
+        <v>0.116s</v>
       </c>
       <c r="M54" t="str">
         <v>N/A</v>
@@ -2876,7 +2876,7 @@
         <v>PASS</v>
       </c>
       <c r="L55" t="str">
-        <v>0.074s</v>
+        <v>0.081s</v>
       </c>
       <c r="M55" t="str">
         <v>N/A</v>
@@ -2919,7 +2919,7 @@
         <v>PASS</v>
       </c>
       <c r="L56" t="str">
-        <v>0.081s</v>
+        <v>0.088s</v>
       </c>
       <c r="M56" t="str">
         <v>N/A</v>
@@ -2962,7 +2962,7 @@
         <v>PASS</v>
       </c>
       <c r="L57" t="str">
-        <v>0.145s</v>
+        <v>0.144s</v>
       </c>
       <c r="M57" t="str">
         <v>N/A</v>
@@ -3005,7 +3005,7 @@
         <v>PASS</v>
       </c>
       <c r="L58" t="str">
-        <v>0.160s</v>
+        <v>0.108s</v>
       </c>
       <c r="M58" t="str">
         <v>N/A</v>
@@ -3048,7 +3048,7 @@
         <v>PASS</v>
       </c>
       <c r="L59" t="str">
-        <v>0.148s</v>
+        <v>0.050s</v>
       </c>
       <c r="M59" t="str">
         <v>N/A</v>
@@ -3091,7 +3091,7 @@
         <v>PASS</v>
       </c>
       <c r="L60" t="str">
-        <v>0.081s</v>
+        <v>0.076s</v>
       </c>
       <c r="M60" t="str">
         <v>N/A</v>
@@ -3134,7 +3134,7 @@
         <v>PASS</v>
       </c>
       <c r="L61" t="str">
-        <v>0.091s</v>
+        <v>0.069s</v>
       </c>
       <c r="M61" t="str">
         <v>N/A</v>
@@ -3177,7 +3177,7 @@
         <v>PASS</v>
       </c>
       <c r="L62" t="str">
-        <v>0.096s</v>
+        <v>0.120s</v>
       </c>
       <c r="M62" t="str">
         <v>N/A</v>
@@ -3220,7 +3220,7 @@
         <v>PASS</v>
       </c>
       <c r="L63" t="str">
-        <v>0.050s</v>
+        <v>0.099s</v>
       </c>
       <c r="M63" t="str">
         <v>N/A</v>
@@ -3263,7 +3263,7 @@
         <v>PASS</v>
       </c>
       <c r="L64" t="str">
-        <v>0.134s</v>
+        <v>0.105s</v>
       </c>
       <c r="M64" t="str">
         <v>N/A</v>
@@ -3306,7 +3306,7 @@
         <v>PASS</v>
       </c>
       <c r="L65" t="str">
-        <v>0.044s</v>
+        <v>0.112s</v>
       </c>
       <c r="M65" t="str">
         <v>N/A</v>
@@ -3349,7 +3349,7 @@
         <v>PASS</v>
       </c>
       <c r="L66" t="str">
-        <v>0.155s</v>
+        <v>0.123s</v>
       </c>
       <c r="M66" t="str">
         <v>N/A</v>
@@ -3392,7 +3392,7 @@
         <v>PASS</v>
       </c>
       <c r="L67" t="str">
-        <v>0.064s</v>
+        <v>0.141s</v>
       </c>
       <c r="M67" t="str">
         <v>N/A</v>
@@ -3435,7 +3435,7 @@
         <v>PASS</v>
       </c>
       <c r="L68" t="str">
-        <v>0.141s</v>
+        <v>0.130s</v>
       </c>
       <c r="M68" t="str">
         <v>N/A</v>
@@ -3478,7 +3478,7 @@
         <v>PASS</v>
       </c>
       <c r="L69" t="str">
-        <v>0.112s</v>
+        <v>0.159s</v>
       </c>
       <c r="M69" t="str">
         <v>N/A</v>
@@ -3521,7 +3521,7 @@
         <v>PASS</v>
       </c>
       <c r="L70" t="str">
-        <v>0.148s</v>
+        <v>0.103s</v>
       </c>
       <c r="M70" t="str">
         <v>N/A</v>
@@ -3564,7 +3564,7 @@
         <v>PASS</v>
       </c>
       <c r="L71" t="str">
-        <v>0.078s</v>
+        <v>0.046s</v>
       </c>
       <c r="M71" t="str">
         <v>N/A</v>
@@ -3607,7 +3607,7 @@
         <v>PASS</v>
       </c>
       <c r="L72" t="str">
-        <v>0.103s</v>
+        <v>0.136s</v>
       </c>
       <c r="M72" t="str">
         <v>N/A</v>
@@ -3650,7 +3650,7 @@
         <v>PASS</v>
       </c>
       <c r="L73" t="str">
-        <v>0.127s</v>
+        <v>0.078s</v>
       </c>
       <c r="M73" t="str">
         <v>N/A</v>
@@ -3693,7 +3693,7 @@
         <v>PASS</v>
       </c>
       <c r="L74" t="str">
-        <v>0.126s</v>
+        <v>0.132s</v>
       </c>
       <c r="M74" t="str">
         <v>N/A</v>
@@ -3736,7 +3736,7 @@
         <v>PASS</v>
       </c>
       <c r="L75" t="str">
-        <v>0.116s</v>
+        <v>0.155s</v>
       </c>
       <c r="M75" t="str">
         <v>N/A</v>
@@ -3779,7 +3779,7 @@
         <v>PASS</v>
       </c>
       <c r="L76" t="str">
-        <v>0.120s</v>
+        <v>0.065s</v>
       </c>
       <c r="M76" t="str">
         <v>N/A</v>
@@ -3822,7 +3822,7 @@
         <v>PASS</v>
       </c>
       <c r="L77" t="str">
-        <v>0.131s</v>
+        <v>0.142s</v>
       </c>
       <c r="M77" t="str">
         <v>N/A</v>
@@ -3865,7 +3865,7 @@
         <v>PASS</v>
       </c>
       <c r="L78" t="str">
-        <v>0.047s</v>
+        <v>0.143s</v>
       </c>
       <c r="M78" t="str">
         <v>N/A</v>
@@ -3908,7 +3908,7 @@
         <v>PASS</v>
       </c>
       <c r="L79" t="str">
-        <v>0.107s</v>
+        <v>0.109s</v>
       </c>
       <c r="M79" t="str">
         <v>N/A</v>
@@ -3951,7 +3951,7 @@
         <v>PASS</v>
       </c>
       <c r="L80" t="str">
-        <v>0.144s</v>
+        <v>0.077s</v>
       </c>
       <c r="M80" t="str">
         <v>N/A</v>
@@ -3994,7 +3994,7 @@
         <v>PASS</v>
       </c>
       <c r="L81" t="str">
-        <v>0.077s</v>
+        <v>0.105s</v>
       </c>
       <c r="M81" t="str">
         <v>N/A</v>
@@ -4037,7 +4037,7 @@
         <v>PASS</v>
       </c>
       <c r="L82" t="str">
-        <v>0.145s</v>
+        <v>0.048s</v>
       </c>
       <c r="M82" t="str">
         <v>N/A</v>
@@ -4080,7 +4080,7 @@
         <v>PASS</v>
       </c>
       <c r="L83" t="str">
-        <v>0.139s</v>
+        <v>0.143s</v>
       </c>
       <c r="M83" t="str">
         <v>N/A</v>
@@ -4123,7 +4123,7 @@
         <v>PASS</v>
       </c>
       <c r="L84" t="str">
-        <v>0.044s</v>
+        <v>0.103s</v>
       </c>
       <c r="M84" t="str">
         <v>N/A</v>
@@ -4166,7 +4166,7 @@
         <v>PASS</v>
       </c>
       <c r="L85" t="str">
-        <v>0.130s</v>
+        <v>0.104s</v>
       </c>
       <c r="M85" t="str">
         <v>N/A</v>
@@ -4209,7 +4209,7 @@
         <v>PASS</v>
       </c>
       <c r="L86" t="str">
-        <v>0.140s</v>
+        <v>0.097s</v>
       </c>
       <c r="M86" t="str">
         <v>N/A</v>
@@ -4252,7 +4252,7 @@
         <v>PASS</v>
       </c>
       <c r="L87" t="str">
-        <v>0.136s</v>
+        <v>0.124s</v>
       </c>
       <c r="M87" t="str">
         <v>N/A</v>
@@ -4295,7 +4295,7 @@
         <v>PASS</v>
       </c>
       <c r="L88" t="str">
-        <v>0.094s</v>
+        <v>0.093s</v>
       </c>
       <c r="M88" t="str">
         <v>N/A</v>
@@ -4338,7 +4338,7 @@
         <v>PASS</v>
       </c>
       <c r="L89" t="str">
-        <v>0.133s</v>
+        <v>0.066s</v>
       </c>
       <c r="M89" t="str">
         <v>N/A</v>
@@ -4381,7 +4381,7 @@
         <v>PASS</v>
       </c>
       <c r="L90" t="str">
-        <v>0.085s</v>
+        <v>0.146s</v>
       </c>
       <c r="M90" t="str">
         <v>N/A</v>
@@ -4424,7 +4424,7 @@
         <v>PASS</v>
       </c>
       <c r="L91" t="str">
-        <v>0.065s</v>
+        <v>0.132s</v>
       </c>
       <c r="M91" t="str">
         <v>N/A</v>
@@ -4467,7 +4467,7 @@
         <v>PASS</v>
       </c>
       <c r="L92" t="str">
-        <v>0.052s</v>
+        <v>0.057s</v>
       </c>
       <c r="M92" t="str">
         <v>N/A</v>
@@ -4510,7 +4510,7 @@
         <v>PASS</v>
       </c>
       <c r="L93" t="str">
-        <v>0.074s</v>
+        <v>0.130s</v>
       </c>
       <c r="M93" t="str">
         <v>N/A</v>
@@ -4553,7 +4553,7 @@
         <v>PASS</v>
       </c>
       <c r="L94" t="str">
-        <v>0.124s</v>
+        <v>0.094s</v>
       </c>
       <c r="M94" t="str">
         <v>N/A</v>
@@ -4596,7 +4596,7 @@
         <v>PASS</v>
       </c>
       <c r="L95" t="str">
-        <v>0.154s</v>
+        <v>0.084s</v>
       </c>
       <c r="M95" t="str">
         <v>N/A</v>
@@ -4639,7 +4639,7 @@
         <v>PASS</v>
       </c>
       <c r="L96" t="str">
-        <v>0.122s</v>
+        <v>0.098s</v>
       </c>
       <c r="M96" t="str">
         <v>N/A</v>
@@ -4682,7 +4682,7 @@
         <v>PASS</v>
       </c>
       <c r="L97" t="str">
-        <v>0.063s</v>
+        <v>0.108s</v>
       </c>
       <c r="M97" t="str">
         <v>N/A</v>
@@ -4725,7 +4725,7 @@
         <v>PASS</v>
       </c>
       <c r="L98" t="str">
-        <v>0.092s</v>
+        <v>0.053s</v>
       </c>
       <c r="M98" t="str">
         <v>N/A</v>
@@ -4768,7 +4768,7 @@
         <v>PASS</v>
       </c>
       <c r="L99" t="str">
-        <v>0.120s</v>
+        <v>0.067s</v>
       </c>
       <c r="M99" t="str">
         <v>N/A</v>
@@ -4811,7 +4811,7 @@
         <v>PASS</v>
       </c>
       <c r="L100" t="str">
-        <v>0.134s</v>
+        <v>0.070s</v>
       </c>
       <c r="M100" t="str">
         <v>N/A</v>
@@ -4854,7 +4854,7 @@
         <v>PASS</v>
       </c>
       <c r="L101" t="str">
-        <v>0.157s</v>
+        <v>0.145s</v>
       </c>
       <c r="M101" t="str">
         <v>N/A</v>
@@ -4897,7 +4897,7 @@
         <v>PASS</v>
       </c>
       <c r="L102" t="str">
-        <v>0.085s</v>
+        <v>0.063s</v>
       </c>
       <c r="M102" t="str">
         <v>N/A</v>
@@ -4940,7 +4940,7 @@
         <v>PASS</v>
       </c>
       <c r="L103" t="str">
-        <v>0.096s</v>
+        <v>0.113s</v>
       </c>
       <c r="M103" t="str">
         <v>N/A</v>
@@ -4983,7 +4983,7 @@
         <v>PASS</v>
       </c>
       <c r="L104" t="str">
-        <v>0.089s</v>
+        <v>0.045s</v>
       </c>
       <c r="M104" t="str">
         <v>N/A</v>
@@ -5026,7 +5026,7 @@
         <v>PASS</v>
       </c>
       <c r="L105" t="str">
-        <v>0.107s</v>
+        <v>0.134s</v>
       </c>
       <c r="M105" t="str">
         <v>N/A</v>
@@ -5069,7 +5069,7 @@
         <v>PASS</v>
       </c>
       <c r="L106" t="str">
-        <v>0.081s</v>
+        <v>0.152s</v>
       </c>
       <c r="M106" t="str">
         <v>N/A</v>
@@ -5112,7 +5112,7 @@
         <v>PASS</v>
       </c>
       <c r="L107" t="str">
-        <v>0.090s</v>
+        <v>0.107s</v>
       </c>
       <c r="M107" t="str">
         <v>N/A</v>
@@ -5155,7 +5155,7 @@
         <v>PASS</v>
       </c>
       <c r="L108" t="str">
-        <v>0.131s</v>
+        <v>0.068s</v>
       </c>
       <c r="M108" t="str">
         <v>N/A</v>
@@ -5198,7 +5198,7 @@
         <v>PASS</v>
       </c>
       <c r="L109" t="str">
-        <v>0.155s</v>
+        <v>0.146s</v>
       </c>
       <c r="M109" t="str">
         <v>N/A</v>
@@ -5241,7 +5241,7 @@
         <v>PASS</v>
       </c>
       <c r="L110" t="str">
-        <v>0.150s</v>
+        <v>0.064s</v>
       </c>
       <c r="M110" t="str">
         <v>N/A</v>
@@ -5284,7 +5284,7 @@
         <v>PASS</v>
       </c>
       <c r="L111" t="str">
-        <v>0.143s</v>
+        <v>0.062s</v>
       </c>
       <c r="M111" t="str">
         <v>N/A</v>
@@ -5327,7 +5327,7 @@
         <v>PASS</v>
       </c>
       <c r="L112" t="str">
-        <v>0.067s</v>
+        <v>0.142s</v>
       </c>
       <c r="M112" t="str">
         <v>N/A</v>
@@ -5370,7 +5370,7 @@
         <v>PASS</v>
       </c>
       <c r="L113" t="str">
-        <v>0.110s</v>
+        <v>0.048s</v>
       </c>
       <c r="M113" t="str">
         <v>N/A</v>
@@ -5413,7 +5413,7 @@
         <v>PASS</v>
       </c>
       <c r="L114" t="str">
-        <v>0.074s</v>
+        <v>0.120s</v>
       </c>
       <c r="M114" t="str">
         <v>N/A</v>
@@ -5456,7 +5456,7 @@
         <v>PASS</v>
       </c>
       <c r="L115" t="str">
-        <v>0.132s</v>
+        <v>0.064s</v>
       </c>
       <c r="M115" t="str">
         <v>N/A</v>
@@ -5499,7 +5499,7 @@
         <v>PASS</v>
       </c>
       <c r="L116" t="str">
-        <v>0.083s</v>
+        <v>0.138s</v>
       </c>
       <c r="M116" t="str">
         <v>N/A</v>
@@ -5542,7 +5542,7 @@
         <v>PASS</v>
       </c>
       <c r="L117" t="str">
-        <v>0.057s</v>
+        <v>0.155s</v>
       </c>
       <c r="M117" t="str">
         <v>N/A</v>
@@ -5585,7 +5585,7 @@
         <v>PASS</v>
       </c>
       <c r="L118" t="str">
-        <v>0.146s</v>
+        <v>0.101s</v>
       </c>
       <c r="M118" t="str">
         <v>N/A</v>
@@ -5628,7 +5628,7 @@
         <v>PASS</v>
       </c>
       <c r="L119" t="str">
-        <v>0.043s</v>
+        <v>0.078s</v>
       </c>
       <c r="M119" t="str">
         <v>N/A</v>
@@ -5671,7 +5671,7 @@
         <v>PASS</v>
       </c>
       <c r="L120" t="str">
-        <v>0.113s</v>
+        <v>0.100s</v>
       </c>
       <c r="M120" t="str">
         <v>N/A</v>
@@ -5714,7 +5714,7 @@
         <v>PASS</v>
       </c>
       <c r="L121" t="str">
-        <v>0.151s</v>
+        <v>0.122s</v>
       </c>
       <c r="M121" t="str">
         <v>N/A</v>
@@ -5757,7 +5757,7 @@
         <v>PASS</v>
       </c>
       <c r="L122" t="str">
-        <v>0.102s</v>
+        <v>0.082s</v>
       </c>
       <c r="M122" t="str">
         <v>N/A</v>
@@ -5800,7 +5800,7 @@
         <v>PASS</v>
       </c>
       <c r="L123" t="str">
-        <v>0.127s</v>
+        <v>0.125s</v>
       </c>
       <c r="M123" t="str">
         <v>N/A</v>
@@ -5843,7 +5843,7 @@
         <v>PASS</v>
       </c>
       <c r="L124" t="str">
-        <v>0.107s</v>
+        <v>0.056s</v>
       </c>
       <c r="M124" t="str">
         <v>N/A</v>
@@ -5886,7 +5886,7 @@
         <v>PASS</v>
       </c>
       <c r="L125" t="str">
-        <v>0.071s</v>
+        <v>0.058s</v>
       </c>
       <c r="M125" t="str">
         <v>N/A</v>
@@ -5929,7 +5929,7 @@
         <v>PASS</v>
       </c>
       <c r="L126" t="str">
-        <v>0.135s</v>
+        <v>0.157s</v>
       </c>
       <c r="M126" t="str">
         <v>N/A</v>
@@ -5972,7 +5972,7 @@
         <v>PASS</v>
       </c>
       <c r="L127" t="str">
-        <v>0.042s</v>
+        <v>0.113s</v>
       </c>
       <c r="M127" t="str">
         <v>N/A</v>
@@ -6015,7 +6015,7 @@
         <v>PASS</v>
       </c>
       <c r="L128" t="str">
-        <v>0.129s</v>
+        <v>0.103s</v>
       </c>
       <c r="M128" t="str">
         <v>N/A</v>
@@ -6058,7 +6058,7 @@
         <v>PASS</v>
       </c>
       <c r="L129" t="str">
-        <v>0.073s</v>
+        <v>0.089s</v>
       </c>
       <c r="M129" t="str">
         <v>N/A</v>
@@ -6101,7 +6101,7 @@
         <v>PASS</v>
       </c>
       <c r="L130" t="str">
-        <v>0.159s</v>
+        <v>0.116s</v>
       </c>
       <c r="M130" t="str">
         <v>N/A</v>
@@ -6144,7 +6144,7 @@
         <v>PASS</v>
       </c>
       <c r="L131" t="str">
-        <v>0.084s</v>
+        <v>0.101s</v>
       </c>
       <c r="M131" t="str">
         <v>N/A</v>
@@ -6187,7 +6187,7 @@
         <v>PASS</v>
       </c>
       <c r="L132" t="str">
-        <v>0.141s</v>
+        <v>0.107s</v>
       </c>
       <c r="M132" t="str">
         <v>N/A</v>
@@ -6230,7 +6230,7 @@
         <v>PASS</v>
       </c>
       <c r="L133" t="str">
-        <v>0.114s</v>
+        <v>0.099s</v>
       </c>
       <c r="M133" t="str">
         <v>N/A</v>
@@ -6273,7 +6273,7 @@
         <v>PASS</v>
       </c>
       <c r="L134" t="str">
-        <v>0.079s</v>
+        <v>0.124s</v>
       </c>
       <c r="M134" t="str">
         <v>N/A</v>
@@ -6316,7 +6316,7 @@
         <v>PASS</v>
       </c>
       <c r="L135" t="str">
-        <v>0.138s</v>
+        <v>0.095s</v>
       </c>
       <c r="M135" t="str">
         <v>N/A</v>
@@ -6359,7 +6359,7 @@
         <v>PASS</v>
       </c>
       <c r="L136" t="str">
-        <v>0.071s</v>
+        <v>0.069s</v>
       </c>
       <c r="M136" t="str">
         <v>N/A</v>
@@ -6402,7 +6402,7 @@
         <v>PASS</v>
       </c>
       <c r="L137" t="str">
-        <v>0.073s</v>
+        <v>0.078s</v>
       </c>
       <c r="M137" t="str">
         <v>N/A</v>
@@ -6445,7 +6445,7 @@
         <v>PASS</v>
       </c>
       <c r="L138" t="str">
-        <v>0.062s</v>
+        <v>0.106s</v>
       </c>
       <c r="M138" t="str">
         <v>N/A</v>
@@ -6488,7 +6488,7 @@
         <v>PASS</v>
       </c>
       <c r="L139" t="str">
-        <v>0.085s</v>
+        <v>0.152s</v>
       </c>
       <c r="M139" t="str">
         <v>N/A</v>
@@ -6531,7 +6531,7 @@
         <v>PASS</v>
       </c>
       <c r="L140" t="str">
-        <v>0.048s</v>
+        <v>0.068s</v>
       </c>
       <c r="M140" t="str">
         <v>N/A</v>
@@ -6574,7 +6574,7 @@
         <v>PASS</v>
       </c>
       <c r="L141" t="str">
-        <v>0.130s</v>
+        <v>0.146s</v>
       </c>
       <c r="M141" t="str">
         <v>N/A</v>
@@ -6617,7 +6617,7 @@
         <v>PASS</v>
       </c>
       <c r="L142" t="str">
-        <v>0.158s</v>
+        <v>0.113s</v>
       </c>
       <c r="M142" t="str">
         <v>N/A</v>
@@ -6660,7 +6660,7 @@
         <v>PASS</v>
       </c>
       <c r="L143" t="str">
-        <v>0.090s</v>
+        <v>0.064s</v>
       </c>
       <c r="M143" t="str">
         <v>N/A</v>
@@ -6703,7 +6703,7 @@
         <v>PASS</v>
       </c>
       <c r="L144" t="str">
-        <v>0.077s</v>
+        <v>0.108s</v>
       </c>
       <c r="M144" t="str">
         <v>N/A</v>
@@ -6746,7 +6746,7 @@
         <v>PASS</v>
       </c>
       <c r="L145" t="str">
-        <v>0.138s</v>
+        <v>0.070s</v>
       </c>
       <c r="M145" t="str">
         <v>N/A</v>
@@ -6789,7 +6789,7 @@
         <v>PASS</v>
       </c>
       <c r="L146" t="str">
-        <v>0.069s</v>
+        <v>0.154s</v>
       </c>
       <c r="M146" t="str">
         <v>N/A</v>
@@ -6832,7 +6832,7 @@
         <v>PASS</v>
       </c>
       <c r="L147" t="str">
-        <v>0.073s</v>
+        <v>0.051s</v>
       </c>
       <c r="M147" t="str">
         <v>N/A</v>
@@ -6875,7 +6875,7 @@
         <v>PASS</v>
       </c>
       <c r="L148" t="str">
-        <v>0.104s</v>
+        <v>0.157s</v>
       </c>
       <c r="M148" t="str">
         <v>N/A</v>
@@ -6918,7 +6918,7 @@
         <v>PASS</v>
       </c>
       <c r="L149" t="str">
-        <v>0.091s</v>
+        <v>0.134s</v>
       </c>
       <c r="M149" t="str">
         <v>N/A</v>
@@ -6961,7 +6961,7 @@
         <v>PASS</v>
       </c>
       <c r="L150" t="str">
-        <v>0.045s</v>
+        <v>0.077s</v>
       </c>
       <c r="M150" t="str">
         <v>N/A</v>
@@ -7004,7 +7004,7 @@
         <v>PASS</v>
       </c>
       <c r="L151" t="str">
-        <v>0.063s</v>
+        <v>0.076s</v>
       </c>
       <c r="M151" t="str">
         <v>N/A</v>
@@ -7047,7 +7047,7 @@
         <v>PASS</v>
       </c>
       <c r="L152" t="str">
-        <v>0.078s</v>
+        <v>0.071s</v>
       </c>
       <c r="M152" t="str">
         <v>N/A</v>
@@ -7090,7 +7090,7 @@
         <v>PASS</v>
       </c>
       <c r="L153" t="str">
-        <v>0.141s</v>
+        <v>0.153s</v>
       </c>
       <c r="M153" t="str">
         <v>N/A</v>
@@ -7133,7 +7133,7 @@
         <v>PASS</v>
       </c>
       <c r="L154" t="str">
-        <v>0.132s</v>
+        <v>0.147s</v>
       </c>
       <c r="M154" t="str">
         <v>N/A</v>
@@ -7176,7 +7176,7 @@
         <v>PASS</v>
       </c>
       <c r="L155" t="str">
-        <v>0.138s</v>
+        <v>0.095s</v>
       </c>
       <c r="M155" t="str">
         <v>N/A</v>
@@ -7219,7 +7219,7 @@
         <v>PASS</v>
       </c>
       <c r="L156" t="str">
-        <v>0.145s</v>
+        <v>0.111s</v>
       </c>
       <c r="M156" t="str">
         <v>N/A</v>
@@ -7262,7 +7262,7 @@
         <v>PASS</v>
       </c>
       <c r="L157" t="str">
-        <v>0.153s</v>
+        <v>0.074s</v>
       </c>
       <c r="M157" t="str">
         <v>N/A</v>
@@ -7305,7 +7305,7 @@
         <v>PASS</v>
       </c>
       <c r="L158" t="str">
-        <v>0.086s</v>
+        <v>0.096s</v>
       </c>
       <c r="M158" t="str">
         <v>N/A</v>
@@ -7348,7 +7348,7 @@
         <v>PASS</v>
       </c>
       <c r="L159" t="str">
-        <v>0.117s</v>
+        <v>0.098s</v>
       </c>
       <c r="M159" t="str">
         <v>N/A</v>
@@ -7391,7 +7391,7 @@
         <v>PASS</v>
       </c>
       <c r="L160" t="str">
-        <v>0.089s</v>
+        <v>0.156s</v>
       </c>
       <c r="M160" t="str">
         <v>N/A</v>
@@ -7434,7 +7434,7 @@
         <v>PASS</v>
       </c>
       <c r="L161" t="str">
-        <v>0.134s</v>
+        <v>0.152s</v>
       </c>
       <c r="M161" t="str">
         <v>N/A</v>
@@ -7477,7 +7477,7 @@
         <v>PASS</v>
       </c>
       <c r="L162" t="str">
-        <v>0.085s</v>
+        <v>0.153s</v>
       </c>
       <c r="M162" t="str">
         <v>N/A</v>
@@ -7520,7 +7520,7 @@
         <v>PASS</v>
       </c>
       <c r="L163" t="str">
-        <v>0.102s</v>
+        <v>0.123s</v>
       </c>
       <c r="M163" t="str">
         <v>N/A</v>
@@ -7563,7 +7563,7 @@
         <v>PASS</v>
       </c>
       <c r="L164" t="str">
-        <v>0.070s</v>
+        <v>0.095s</v>
       </c>
       <c r="M164" t="str">
         <v>N/A</v>
@@ -7606,7 +7606,7 @@
         <v>PASS</v>
       </c>
       <c r="L165" t="str">
-        <v>0.060s</v>
+        <v>0.129s</v>
       </c>
       <c r="M165" t="str">
         <v>N/A</v>
@@ -7649,7 +7649,7 @@
         <v>PASS</v>
       </c>
       <c r="L166" t="str">
-        <v>0.095s</v>
+        <v>0.105s</v>
       </c>
       <c r="M166" t="str">
         <v>N/A</v>
@@ -7692,7 +7692,7 @@
         <v>PASS</v>
       </c>
       <c r="L167" t="str">
-        <v>0.158s</v>
+        <v>0.071s</v>
       </c>
       <c r="M167" t="str">
         <v>N/A</v>
@@ -7735,7 +7735,7 @@
         <v>PASS</v>
       </c>
       <c r="L168" t="str">
-        <v>0.082s</v>
+        <v>0.129s</v>
       </c>
       <c r="M168" t="str">
         <v>N/A</v>
@@ -7778,7 +7778,7 @@
         <v>PASS</v>
       </c>
       <c r="L169" t="str">
-        <v>0.079s</v>
+        <v>0.042s</v>
       </c>
       <c r="M169" t="str">
         <v>N/A</v>
@@ -7821,7 +7821,7 @@
         <v>PASS</v>
       </c>
       <c r="L170" t="str">
-        <v>0.159s</v>
+        <v>0.091s</v>
       </c>
       <c r="M170" t="str">
         <v>N/A</v>
@@ -7864,7 +7864,7 @@
         <v>PASS</v>
       </c>
       <c r="L171" t="str">
-        <v>0.053s</v>
+        <v>0.073s</v>
       </c>
       <c r="M171" t="str">
         <v>N/A</v>
@@ -7907,7 +7907,7 @@
         <v>PASS</v>
       </c>
       <c r="L172" t="str">
-        <v>0.046s</v>
+        <v>0.096s</v>
       </c>
       <c r="M172" t="str">
         <v>N/A</v>
@@ -7950,7 +7950,7 @@
         <v>PASS</v>
       </c>
       <c r="L173" t="str">
-        <v>0.083s</v>
+        <v>0.082s</v>
       </c>
       <c r="M173" t="str">
         <v>N/A</v>
@@ -7993,7 +7993,7 @@
         <v>PASS</v>
       </c>
       <c r="L174" t="str">
-        <v>0.088s</v>
+        <v>0.116s</v>
       </c>
       <c r="M174" t="str">
         <v>N/A</v>
@@ -8036,7 +8036,7 @@
         <v>PASS</v>
       </c>
       <c r="L175" t="str">
-        <v>0.054s</v>
+        <v>0.144s</v>
       </c>
       <c r="M175" t="str">
         <v>N/A</v>
@@ -8079,7 +8079,7 @@
         <v>PASS</v>
       </c>
       <c r="L176" t="str">
-        <v>0.111s</v>
+        <v>0.051s</v>
       </c>
       <c r="M176" t="str">
         <v>N/A</v>
@@ -8122,7 +8122,7 @@
         <v>PASS</v>
       </c>
       <c r="L177" t="str">
-        <v>0.132s</v>
+        <v>0.093s</v>
       </c>
       <c r="M177" t="str">
         <v>N/A</v>
@@ -8165,7 +8165,7 @@
         <v>PASS</v>
       </c>
       <c r="L178" t="str">
-        <v>0.116s</v>
+        <v>0.059s</v>
       </c>
       <c r="M178" t="str">
         <v>N/A</v>
@@ -8208,7 +8208,7 @@
         <v>PASS</v>
       </c>
       <c r="L179" t="str">
-        <v>0.082s</v>
+        <v>0.147s</v>
       </c>
       <c r="M179" t="str">
         <v>N/A</v>
@@ -8251,7 +8251,7 @@
         <v>PASS</v>
       </c>
       <c r="L180" t="str">
-        <v>0.053s</v>
+        <v>0.154s</v>
       </c>
       <c r="M180" t="str">
         <v>N/A</v>
@@ -8294,7 +8294,7 @@
         <v>PASS</v>
       </c>
       <c r="L181" t="str">
-        <v>0.120s</v>
+        <v>0.092s</v>
       </c>
       <c r="M181" t="str">
         <v>N/A</v>
@@ -8337,7 +8337,7 @@
         <v>PASS</v>
       </c>
       <c r="L182" t="str">
-        <v>0.058s</v>
+        <v>0.066s</v>
       </c>
       <c r="M182" t="str">
         <v>N/A</v>
@@ -8380,7 +8380,7 @@
         <v>PASS</v>
       </c>
       <c r="L183" t="str">
-        <v>0.042s</v>
+        <v>0.051s</v>
       </c>
       <c r="M183" t="str">
         <v>N/A</v>
@@ -8423,7 +8423,7 @@
         <v>PASS</v>
       </c>
       <c r="L184" t="str">
-        <v>0.101s</v>
+        <v>0.138s</v>
       </c>
       <c r="M184" t="str">
         <v>N/A</v>
@@ -8466,7 +8466,7 @@
         <v>PASS</v>
       </c>
       <c r="L185" t="str">
-        <v>0.047s</v>
+        <v>0.074s</v>
       </c>
       <c r="M185" t="str">
         <v>N/A</v>
@@ -8509,7 +8509,7 @@
         <v>PASS</v>
       </c>
       <c r="L186" t="str">
-        <v>0.081s</v>
+        <v>0.099s</v>
       </c>
       <c r="M186" t="str">
         <v>N/A</v>
@@ -8552,7 +8552,7 @@
         <v>PASS</v>
       </c>
       <c r="L187" t="str">
-        <v>0.069s</v>
+        <v>0.046s</v>
       </c>
       <c r="M187" t="str">
         <v>N/A</v>
@@ -8595,7 +8595,7 @@
         <v>PASS</v>
       </c>
       <c r="L188" t="str">
-        <v>0.052s</v>
+        <v>0.082s</v>
       </c>
       <c r="M188" t="str">
         <v>N/A</v>
@@ -8638,7 +8638,7 @@
         <v>PASS</v>
       </c>
       <c r="L189" t="str">
-        <v>0.107s</v>
+        <v>0.149s</v>
       </c>
       <c r="M189" t="str">
         <v>N/A</v>
@@ -8681,7 +8681,7 @@
         <v>PASS</v>
       </c>
       <c r="L190" t="str">
-        <v>0.123s</v>
+        <v>0.112s</v>
       </c>
       <c r="M190" t="str">
         <v>N/A</v>
@@ -8724,7 +8724,7 @@
         <v>PASS</v>
       </c>
       <c r="L191" t="str">
-        <v>0.089s</v>
+        <v>0.045s</v>
       </c>
       <c r="M191" t="str">
         <v>N/A</v>
@@ -8767,7 +8767,7 @@
         <v>PASS</v>
       </c>
       <c r="L192" t="str">
-        <v>0.158s</v>
+        <v>0.144s</v>
       </c>
       <c r="M192" t="str">
         <v>N/A</v>
@@ -8810,7 +8810,7 @@
         <v>PASS</v>
       </c>
       <c r="L193" t="str">
-        <v>0.138s</v>
+        <v>0.062s</v>
       </c>
       <c r="M193" t="str">
         <v>N/A</v>
@@ -8853,7 +8853,7 @@
         <v>PASS</v>
       </c>
       <c r="L194" t="str">
-        <v>0.061s</v>
+        <v>0.114s</v>
       </c>
       <c r="M194" t="str">
         <v>N/A</v>
@@ -8896,7 +8896,7 @@
         <v>PASS</v>
       </c>
       <c r="L195" t="str">
-        <v>0.145s</v>
+        <v>0.103s</v>
       </c>
       <c r="M195" t="str">
         <v>N/A</v>
@@ -8939,7 +8939,7 @@
         <v>PASS</v>
       </c>
       <c r="L196" t="str">
-        <v>0.087s</v>
+        <v>0.047s</v>
       </c>
       <c r="M196" t="str">
         <v>N/A</v>
@@ -8982,7 +8982,7 @@
         <v>PASS</v>
       </c>
       <c r="L197" t="str">
-        <v>0.103s</v>
+        <v>0.111s</v>
       </c>
       <c r="M197" t="str">
         <v>N/A</v>
@@ -9025,7 +9025,7 @@
         <v>PASS</v>
       </c>
       <c r="L198" t="str">
-        <v>0.124s</v>
+        <v>0.126s</v>
       </c>
       <c r="M198" t="str">
         <v>N/A</v>
@@ -9068,7 +9068,7 @@
         <v>PASS</v>
       </c>
       <c r="L199" t="str">
-        <v>0.143s</v>
+        <v>0.065s</v>
       </c>
       <c r="M199" t="str">
         <v>N/A</v>
@@ -9111,7 +9111,7 @@
         <v>PASS</v>
       </c>
       <c r="L200" t="str">
-        <v>0.141s</v>
+        <v>0.061s</v>
       </c>
       <c r="M200" t="str">
         <v>N/A</v>
@@ -9154,7 +9154,7 @@
         <v>PASS</v>
       </c>
       <c r="L201" t="str">
-        <v>0.041s</v>
+        <v>0.065s</v>
       </c>
       <c r="M201" t="str">
         <v>N/A</v>
@@ -9197,7 +9197,7 @@
         <v>PASS</v>
       </c>
       <c r="L202" t="str">
-        <v>0.042s</v>
+        <v>0.156s</v>
       </c>
       <c r="M202" t="str">
         <v>N/A</v>
@@ -9240,7 +9240,7 @@
         <v>PASS</v>
       </c>
       <c r="L203" t="str">
-        <v>0.110s</v>
+        <v>0.047s</v>
       </c>
       <c r="M203" t="str">
         <v>N/A</v>
@@ -9283,7 +9283,7 @@
         <v>PASS</v>
       </c>
       <c r="L204" t="str">
-        <v>0.135s</v>
+        <v>0.098s</v>
       </c>
       <c r="M204" t="str">
         <v>N/A</v>
@@ -9326,7 +9326,7 @@
         <v>PASS</v>
       </c>
       <c r="L205" t="str">
-        <v>0.063s</v>
+        <v>0.132s</v>
       </c>
       <c r="M205" t="str">
         <v>N/A</v>
@@ -9369,7 +9369,7 @@
         <v>PASS</v>
       </c>
       <c r="L206" t="str">
-        <v>0.145s</v>
+        <v>0.150s</v>
       </c>
       <c r="M206" t="str">
         <v>N/A</v>
@@ -9412,7 +9412,7 @@
         <v>PASS</v>
       </c>
       <c r="L207" t="str">
-        <v>0.094s</v>
+        <v>0.136s</v>
       </c>
       <c r="M207" t="str">
         <v>N/A</v>
@@ -9455,7 +9455,7 @@
         <v>PASS</v>
       </c>
       <c r="L208" t="str">
-        <v>0.152s</v>
+        <v>0.073s</v>
       </c>
       <c r="M208" t="str">
         <v>N/A</v>
@@ -9498,7 +9498,7 @@
         <v>PASS</v>
       </c>
       <c r="L209" t="str">
-        <v>0.077s</v>
+        <v>0.118s</v>
       </c>
       <c r="M209" t="str">
         <v>N/A</v>
@@ -9541,7 +9541,7 @@
         <v>PASS</v>
       </c>
       <c r="L210" t="str">
-        <v>0.128s</v>
+        <v>0.052s</v>
       </c>
       <c r="M210" t="str">
         <v>N/A</v>
@@ -9584,7 +9584,7 @@
         <v>PASS</v>
       </c>
       <c r="L211" t="str">
-        <v>0.121s</v>
+        <v>0.053s</v>
       </c>
       <c r="M211" t="str">
         <v>N/A</v>
@@ -9627,7 +9627,7 @@
         <v>PASS</v>
       </c>
       <c r="L212" t="str">
-        <v>0.154s</v>
+        <v>0.045s</v>
       </c>
       <c r="M212" t="str">
         <v>N/A</v>
@@ -9670,7 +9670,7 @@
         <v>PASS</v>
       </c>
       <c r="L213" t="str">
-        <v>0.128s</v>
+        <v>0.144s</v>
       </c>
       <c r="M213" t="str">
         <v>N/A</v>
@@ -9713,7 +9713,7 @@
         <v>PASS</v>
       </c>
       <c r="L214" t="str">
-        <v>0.135s</v>
+        <v>0.137s</v>
       </c>
       <c r="M214" t="str">
         <v>N/A</v>
@@ -9756,7 +9756,7 @@
         <v>PASS</v>
       </c>
       <c r="L215" t="str">
-        <v>0.063s</v>
+        <v>0.124s</v>
       </c>
       <c r="M215" t="str">
         <v>N/A</v>
@@ -9799,7 +9799,7 @@
         <v>PASS</v>
       </c>
       <c r="L216" t="str">
-        <v>0.107s</v>
+        <v>0.090s</v>
       </c>
       <c r="M216" t="str">
         <v>N/A</v>
@@ -9842,7 +9842,7 @@
         <v>PASS</v>
       </c>
       <c r="L217" t="str">
-        <v>0.074s</v>
+        <v>0.050s</v>
       </c>
       <c r="M217" t="str">
         <v>N/A</v>
@@ -9885,7 +9885,7 @@
         <v>PASS</v>
       </c>
       <c r="L218" t="str">
-        <v>0.127s</v>
+        <v>0.158s</v>
       </c>
       <c r="M218" t="str">
         <v>N/A</v>
@@ -9928,7 +9928,7 @@
         <v>PASS</v>
       </c>
       <c r="L219" t="str">
-        <v>0.139s</v>
+        <v>0.128s</v>
       </c>
       <c r="M219" t="str">
         <v>N/A</v>
@@ -9971,7 +9971,7 @@
         <v>PASS</v>
       </c>
       <c r="L220" t="str">
-        <v>0.149s</v>
+        <v>0.086s</v>
       </c>
       <c r="M220" t="str">
         <v>N/A</v>
@@ -10014,7 +10014,7 @@
         <v>PASS</v>
       </c>
       <c r="L221" t="str">
-        <v>0.133s</v>
+        <v>0.155s</v>
       </c>
       <c r="M221" t="str">
         <v>N/A</v>
@@ -10057,7 +10057,7 @@
         <v>PASS</v>
       </c>
       <c r="L222" t="str">
-        <v>0.085s</v>
+        <v>0.048s</v>
       </c>
       <c r="M222" t="str">
         <v>N/A</v>
@@ -10100,7 +10100,7 @@
         <v>PASS</v>
       </c>
       <c r="L223" t="str">
-        <v>0.148s</v>
+        <v>0.118s</v>
       </c>
       <c r="M223" t="str">
         <v>N/A</v>
@@ -10143,7 +10143,7 @@
         <v>PASS</v>
       </c>
       <c r="L224" t="str">
-        <v>0.108s</v>
+        <v>0.140s</v>
       </c>
       <c r="M224" t="str">
         <v>N/A</v>
@@ -10186,7 +10186,7 @@
         <v>PASS</v>
       </c>
       <c r="L225" t="str">
-        <v>0.095s</v>
+        <v>0.045s</v>
       </c>
       <c r="M225" t="str">
         <v>N/A</v>
@@ -10229,7 +10229,7 @@
         <v>PASS</v>
       </c>
       <c r="L226" t="str">
-        <v>0.079s</v>
+        <v>0.159s</v>
       </c>
       <c r="M226" t="str">
         <v>N/A</v>
@@ -10272,7 +10272,7 @@
         <v>PASS</v>
       </c>
       <c r="L227" t="str">
-        <v>0.100s</v>
+        <v>0.073s</v>
       </c>
       <c r="M227" t="str">
         <v>N/A</v>
@@ -10315,7 +10315,7 @@
         <v>PASS</v>
       </c>
       <c r="L228" t="str">
-        <v>0.124s</v>
+        <v>0.146s</v>
       </c>
       <c r="M228" t="str">
         <v>N/A</v>
@@ -10358,7 +10358,7 @@
         <v>PASS</v>
       </c>
       <c r="L229" t="str">
-        <v>0.141s</v>
+        <v>0.058s</v>
       </c>
       <c r="M229" t="str">
         <v>N/A</v>
@@ -10401,7 +10401,7 @@
         <v>PASS</v>
       </c>
       <c r="L230" t="str">
-        <v>0.124s</v>
+        <v>0.153s</v>
       </c>
       <c r="M230" t="str">
         <v>N/A</v>
@@ -10487,7 +10487,7 @@
         <v>PASS</v>
       </c>
       <c r="L232" t="str">
-        <v>0.150s</v>
+        <v>0.075s</v>
       </c>
       <c r="M232" t="str">
         <v>N/A</v>
@@ -10530,7 +10530,7 @@
         <v>PASS</v>
       </c>
       <c r="L233" t="str">
-        <v>0.120s</v>
+        <v>0.087s</v>
       </c>
       <c r="M233" t="str">
         <v>N/A</v>
@@ -10573,7 +10573,7 @@
         <v>PASS</v>
       </c>
       <c r="L234" t="str">
-        <v>0.052s</v>
+        <v>0.120s</v>
       </c>
       <c r="M234" t="str">
         <v>N/A</v>
@@ -10616,7 +10616,7 @@
         <v>PASS</v>
       </c>
       <c r="L235" t="str">
-        <v>0.085s</v>
+        <v>0.040s</v>
       </c>
       <c r="M235" t="str">
         <v>N/A</v>
@@ -10659,7 +10659,7 @@
         <v>PASS</v>
       </c>
       <c r="L236" t="str">
-        <v>0.081s</v>
+        <v>0.099s</v>
       </c>
       <c r="M236" t="str">
         <v>N/A</v>
@@ -10702,7 +10702,7 @@
         <v>PASS</v>
       </c>
       <c r="L237" t="str">
-        <v>0.060s</v>
+        <v>0.126s</v>
       </c>
       <c r="M237" t="str">
         <v>N/A</v>
@@ -10745,7 +10745,7 @@
         <v>PASS</v>
       </c>
       <c r="L238" t="str">
-        <v>0.100s</v>
+        <v>0.118s</v>
       </c>
       <c r="M238" t="str">
         <v>N/A</v>
@@ -10788,7 +10788,7 @@
         <v>PASS</v>
       </c>
       <c r="L239" t="str">
-        <v>0.151s</v>
+        <v>0.056s</v>
       </c>
       <c r="M239" t="str">
         <v>N/A</v>
@@ -10831,7 +10831,7 @@
         <v>PASS</v>
       </c>
       <c r="L240" t="str">
-        <v>0.072s</v>
+        <v>0.141s</v>
       </c>
       <c r="M240" t="str">
         <v>N/A</v>
@@ -10874,7 +10874,7 @@
         <v>PASS</v>
       </c>
       <c r="L241" t="str">
-        <v>0.054s</v>
+        <v>0.100s</v>
       </c>
       <c r="M241" t="str">
         <v>N/A</v>
@@ -10917,7 +10917,7 @@
         <v>PASS</v>
       </c>
       <c r="L242" t="str">
-        <v>0.130s</v>
+        <v>0.116s</v>
       </c>
       <c r="M242" t="str">
         <v>N/A</v>
@@ -10960,7 +10960,7 @@
         <v>PASS</v>
       </c>
       <c r="L243" t="str">
-        <v>0.063s</v>
+        <v>0.106s</v>
       </c>
       <c r="M243" t="str">
         <v>N/A</v>
@@ -11003,7 +11003,7 @@
         <v>PASS</v>
       </c>
       <c r="L244" t="str">
-        <v>0.146s</v>
+        <v>0.044s</v>
       </c>
       <c r="M244" t="str">
         <v>N/A</v>
@@ -11046,7 +11046,7 @@
         <v>PASS</v>
       </c>
       <c r="L245" t="str">
-        <v>0.059s</v>
+        <v>0.158s</v>
       </c>
       <c r="M245" t="str">
         <v>N/A</v>
@@ -11089,7 +11089,7 @@
         <v>PASS</v>
       </c>
       <c r="L246" t="str">
-        <v>0.156s</v>
+        <v>0.093s</v>
       </c>
       <c r="M246" t="str">
         <v>N/A</v>
@@ -11132,7 +11132,7 @@
         <v>PASS</v>
       </c>
       <c r="L247" t="str">
-        <v>0.156s</v>
+        <v>0.130s</v>
       </c>
       <c r="M247" t="str">
         <v>N/A</v>
@@ -11175,7 +11175,7 @@
         <v>PASS</v>
       </c>
       <c r="L248" t="str">
-        <v>0.134s</v>
+        <v>0.062s</v>
       </c>
       <c r="M248" t="str">
         <v>N/A</v>
@@ -11218,7 +11218,7 @@
         <v>PASS</v>
       </c>
       <c r="L249" t="str">
-        <v>0.086s</v>
+        <v>0.072s</v>
       </c>
       <c r="M249" t="str">
         <v>N/A</v>
@@ -11261,7 +11261,7 @@
         <v>PASS</v>
       </c>
       <c r="L250" t="str">
-        <v>0.104s</v>
+        <v>0.108s</v>
       </c>
       <c r="M250" t="str">
         <v>N/A</v>
@@ -11304,7 +11304,7 @@
         <v>PASS</v>
       </c>
       <c r="L251" t="str">
-        <v>0.093s</v>
+        <v>0.083s</v>
       </c>
       <c r="M251" t="str">
         <v>N/A</v>
@@ -11347,7 +11347,7 @@
         <v>PASS</v>
       </c>
       <c r="L252" t="str">
-        <v>0.068s</v>
+        <v>0.097s</v>
       </c>
       <c r="M252" t="str">
         <v>N/A</v>
@@ -11390,7 +11390,7 @@
         <v>PASS</v>
       </c>
       <c r="L253" t="str">
-        <v>0.131s</v>
+        <v>0.086s</v>
       </c>
       <c r="M253" t="str">
         <v>N/A</v>
@@ -11433,7 +11433,7 @@
         <v>PASS</v>
       </c>
       <c r="L254" t="str">
-        <v>0.053s</v>
+        <v>0.125s</v>
       </c>
       <c r="M254" t="str">
         <v>N/A</v>
@@ -11476,7 +11476,7 @@
         <v>PASS</v>
       </c>
       <c r="L255" t="str">
-        <v>0.138s</v>
+        <v>0.070s</v>
       </c>
       <c r="M255" t="str">
         <v>N/A</v>
@@ -11519,7 +11519,7 @@
         <v>PASS</v>
       </c>
       <c r="L256" t="str">
-        <v>0.092s</v>
+        <v>0.153s</v>
       </c>
       <c r="M256" t="str">
         <v>N/A</v>
@@ -11562,7 +11562,7 @@
         <v>PASS</v>
       </c>
       <c r="L257" t="str">
-        <v>0.147s</v>
+        <v>0.078s</v>
       </c>
       <c r="M257" t="str">
         <v>N/A</v>
@@ -11605,7 +11605,7 @@
         <v>PASS</v>
       </c>
       <c r="L258" t="str">
-        <v>0.094s</v>
+        <v>0.124s</v>
       </c>
       <c r="M258" t="str">
         <v>N/A</v>
@@ -11648,7 +11648,7 @@
         <v>PASS</v>
       </c>
       <c r="L259" t="str">
-        <v>0.086s</v>
+        <v>0.139s</v>
       </c>
       <c r="M259" t="str">
         <v>N/A</v>
@@ -11691,7 +11691,7 @@
         <v>PASS</v>
       </c>
       <c r="L260" t="str">
-        <v>0.104s</v>
+        <v>0.091s</v>
       </c>
       <c r="M260" t="str">
         <v>N/A</v>
@@ -11734,7 +11734,7 @@
         <v>PASS</v>
       </c>
       <c r="L261" t="str">
-        <v>0.055s</v>
+        <v>0.096s</v>
       </c>
       <c r="M261" t="str">
         <v>N/A</v>
@@ -11777,7 +11777,7 @@
         <v>PASS</v>
       </c>
       <c r="L262" t="str">
-        <v>0.155s</v>
+        <v>0.134s</v>
       </c>
       <c r="M262" t="str">
         <v>N/A</v>
@@ -11820,7 +11820,7 @@
         <v>PASS</v>
       </c>
       <c r="L263" t="str">
-        <v>0.126s</v>
+        <v>0.143s</v>
       </c>
       <c r="M263" t="str">
         <v>N/A</v>
@@ -11863,7 +11863,7 @@
         <v>PASS</v>
       </c>
       <c r="L264" t="str">
-        <v>0.075s</v>
+        <v>0.080s</v>
       </c>
       <c r="M264" t="str">
         <v>N/A</v>
@@ -11906,7 +11906,7 @@
         <v>PASS</v>
       </c>
       <c r="L265" t="str">
-        <v>0.122s</v>
+        <v>0.041s</v>
       </c>
       <c r="M265" t="str">
         <v>N/A</v>
@@ -11949,7 +11949,7 @@
         <v>PASS</v>
       </c>
       <c r="L266" t="str">
-        <v>0.068s</v>
+        <v>0.087s</v>
       </c>
       <c r="M266" t="str">
         <v>N/A</v>
@@ -11992,7 +11992,7 @@
         <v>PASS</v>
       </c>
       <c r="L267" t="str">
-        <v>0.118s</v>
+        <v>0.066s</v>
       </c>
       <c r="M267" t="str">
         <v>N/A</v>
@@ -12035,7 +12035,7 @@
         <v>PASS</v>
       </c>
       <c r="L268" t="str">
-        <v>0.124s</v>
+        <v>0.084s</v>
       </c>
       <c r="M268" t="str">
         <v>N/A</v>
@@ -12078,7 +12078,7 @@
         <v>PASS</v>
       </c>
       <c r="L269" t="str">
-        <v>0.136s</v>
+        <v>0.079s</v>
       </c>
       <c r="M269" t="str">
         <v>N/A</v>
@@ -12121,7 +12121,7 @@
         <v>PASS</v>
       </c>
       <c r="L270" t="str">
-        <v>0.043s</v>
+        <v>0.110s</v>
       </c>
       <c r="M270" t="str">
         <v>N/A</v>
@@ -12164,7 +12164,7 @@
         <v>PASS</v>
       </c>
       <c r="L271" t="str">
-        <v>0.055s</v>
+        <v>0.157s</v>
       </c>
       <c r="M271" t="str">
         <v>N/A</v>
@@ -12207,7 +12207,7 @@
         <v>PASS</v>
       </c>
       <c r="L272" t="str">
-        <v>0.159s</v>
+        <v>0.130s</v>
       </c>
       <c r="M272" t="str">
         <v>N/A</v>
@@ -12250,7 +12250,7 @@
         <v>PASS</v>
       </c>
       <c r="L273" t="str">
-        <v>0.090s</v>
+        <v>0.094s</v>
       </c>
       <c r="M273" t="str">
         <v>N/A</v>
@@ -12293,7 +12293,7 @@
         <v>PASS</v>
       </c>
       <c r="L274" t="str">
-        <v>0.121s</v>
+        <v>0.090s</v>
       </c>
       <c r="M274" t="str">
         <v>N/A</v>
@@ -12336,7 +12336,7 @@
         <v>PASS</v>
       </c>
       <c r="L275" t="str">
-        <v>0.065s</v>
+        <v>0.081s</v>
       </c>
       <c r="M275" t="str">
         <v>N/A</v>
@@ -12379,7 +12379,7 @@
         <v>PASS</v>
       </c>
       <c r="L276" t="str">
-        <v>0.112s</v>
+        <v>0.138s</v>
       </c>
       <c r="M276" t="str">
         <v>N/A</v>
@@ -12422,7 +12422,7 @@
         <v>PASS</v>
       </c>
       <c r="L277" t="str">
-        <v>0.115s</v>
+        <v>0.068s</v>
       </c>
       <c r="M277" t="str">
         <v>N/A</v>
@@ -12465,7 +12465,7 @@
         <v>PASS</v>
       </c>
       <c r="L278" t="str">
-        <v>0.096s</v>
+        <v>0.126s</v>
       </c>
       <c r="M278" t="str">
         <v>N/A</v>
@@ -12508,7 +12508,7 @@
         <v>PASS</v>
       </c>
       <c r="L279" t="str">
-        <v>0.130s</v>
+        <v>0.118s</v>
       </c>
       <c r="M279" t="str">
         <v>N/A</v>
@@ -12551,7 +12551,7 @@
         <v>PASS</v>
       </c>
       <c r="L280" t="str">
-        <v>0.043s</v>
+        <v>0.139s</v>
       </c>
       <c r="M280" t="str">
         <v>N/A</v>
@@ -12594,7 +12594,7 @@
         <v>PASS</v>
       </c>
       <c r="L281" t="str">
-        <v>0.135s</v>
+        <v>0.116s</v>
       </c>
       <c r="M281" t="str">
         <v>N/A</v>
@@ -12637,7 +12637,7 @@
         <v>PASS</v>
       </c>
       <c r="L282" t="str">
-        <v>0.150s</v>
+        <v>0.131s</v>
       </c>
       <c r="M282" t="str">
         <v>N/A</v>
@@ -12680,7 +12680,7 @@
         <v>PASS</v>
       </c>
       <c r="L283" t="str">
-        <v>0.135s</v>
+        <v>0.083s</v>
       </c>
       <c r="M283" t="str">
         <v>N/A</v>
@@ -12723,7 +12723,7 @@
         <v>PASS</v>
       </c>
       <c r="L284" t="str">
-        <v>0.113s</v>
+        <v>0.059s</v>
       </c>
       <c r="M284" t="str">
         <v>N/A</v>
@@ -12766,7 +12766,7 @@
         <v>PASS</v>
       </c>
       <c r="L285" t="str">
-        <v>0.066s</v>
+        <v>0.082s</v>
       </c>
       <c r="M285" t="str">
         <v>N/A</v>
@@ -12809,7 +12809,7 @@
         <v>PASS</v>
       </c>
       <c r="L286" t="str">
-        <v>0.132s</v>
+        <v>0.091s</v>
       </c>
       <c r="M286" t="str">
         <v>N/A</v>
@@ -12852,7 +12852,7 @@
         <v>PASS</v>
       </c>
       <c r="L287" t="str">
-        <v>0.137s</v>
+        <v>0.133s</v>
       </c>
       <c r="M287" t="str">
         <v>N/A</v>
@@ -12895,7 +12895,7 @@
         <v>PASS</v>
       </c>
       <c r="L288" t="str">
-        <v>0.092s</v>
+        <v>0.126s</v>
       </c>
       <c r="M288" t="str">
         <v>N/A</v>
@@ -12938,7 +12938,7 @@
         <v>PASS</v>
       </c>
       <c r="L289" t="str">
-        <v>0.110s</v>
+        <v>0.149s</v>
       </c>
       <c r="M289" t="str">
         <v>N/A</v>
@@ -12981,7 +12981,7 @@
         <v>PASS</v>
       </c>
       <c r="L290" t="str">
-        <v>0.110s</v>
+        <v>0.107s</v>
       </c>
       <c r="M290" t="str">
         <v>N/A</v>
@@ -13024,7 +13024,7 @@
         <v>PASS</v>
       </c>
       <c r="L291" t="str">
-        <v>0.096s</v>
+        <v>0.071s</v>
       </c>
       <c r="M291" t="str">
         <v>N/A</v>
@@ -13067,7 +13067,7 @@
         <v>PASS</v>
       </c>
       <c r="L292" t="str">
-        <v>0.078s</v>
+        <v>0.089s</v>
       </c>
       <c r="M292" t="str">
         <v>N/A</v>
@@ -13110,7 +13110,7 @@
         <v>PASS</v>
       </c>
       <c r="L293" t="str">
-        <v>0.070s</v>
+        <v>0.157s</v>
       </c>
       <c r="M293" t="str">
         <v>N/A</v>
@@ -13153,7 +13153,7 @@
         <v>PASS</v>
       </c>
       <c r="L294" t="str">
-        <v>0.134s</v>
+        <v>0.148s</v>
       </c>
       <c r="M294" t="str">
         <v>N/A</v>
@@ -13196,7 +13196,7 @@
         <v>PASS</v>
       </c>
       <c r="L295" t="str">
-        <v>0.132s</v>
+        <v>0.081s</v>
       </c>
       <c r="M295" t="str">
         <v>N/A</v>
@@ -13239,7 +13239,7 @@
         <v>PASS</v>
       </c>
       <c r="L296" t="str">
-        <v>0.100s</v>
+        <v>0.059s</v>
       </c>
       <c r="M296" t="str">
         <v>N/A</v>
@@ -13282,7 +13282,7 @@
         <v>PASS</v>
       </c>
       <c r="L297" t="str">
-        <v>0.066s</v>
+        <v>0.086s</v>
       </c>
       <c r="M297" t="str">
         <v>N/A</v>
@@ -13325,7 +13325,7 @@
         <v>PASS</v>
       </c>
       <c r="L298" t="str">
-        <v>0.124s</v>
+        <v>0.140s</v>
       </c>
       <c r="M298" t="str">
         <v>N/A</v>
@@ -13368,7 +13368,7 @@
         <v>PASS</v>
       </c>
       <c r="L299" t="str">
-        <v>0.125s</v>
+        <v>0.057s</v>
       </c>
       <c r="M299" t="str">
         <v>N/A</v>
@@ -13411,7 +13411,7 @@
         <v>PASS</v>
       </c>
       <c r="L300" t="str">
-        <v>0.073s</v>
+        <v>0.151s</v>
       </c>
       <c r="M300" t="str">
         <v>N/A</v>
@@ -13454,7 +13454,7 @@
         <v>PASS</v>
       </c>
       <c r="L301" t="str">
-        <v>0.158s</v>
+        <v>0.096s</v>
       </c>
       <c r="M301" t="str">
         <v>N/A</v>
@@ -13497,7 +13497,7 @@
         <v>PASS</v>
       </c>
       <c r="L302" t="str">
-        <v>0.054s</v>
+        <v>0.041s</v>
       </c>
       <c r="M302" t="str">
         <v>N/A</v>
@@ -13540,7 +13540,7 @@
         <v>PASS</v>
       </c>
       <c r="L303" t="str">
-        <v>0.109s</v>
+        <v>0.095s</v>
       </c>
       <c r="M303" t="str">
         <v>N/A</v>
@@ -13583,7 +13583,7 @@
         <v>PASS</v>
       </c>
       <c r="L304" t="str">
-        <v>0.140s</v>
+        <v>0.075s</v>
       </c>
       <c r="M304" t="str">
         <v>N/A</v>
@@ -13626,7 +13626,7 @@
         <v>PASS</v>
       </c>
       <c r="L305" t="str">
-        <v>0.111s</v>
+        <v>0.087s</v>
       </c>
       <c r="M305" t="str">
         <v>N/A</v>
@@ -13669,7 +13669,7 @@
         <v>PASS</v>
       </c>
       <c r="L306" t="str">
-        <v>0.073s</v>
+        <v>0.049s</v>
       </c>
       <c r="M306" t="str">
         <v>N/A</v>
@@ -13712,7 +13712,7 @@
         <v>PASS</v>
       </c>
       <c r="L307" t="str">
-        <v>0.046s</v>
+        <v>0.050s</v>
       </c>
       <c r="M307" t="str">
         <v>N/A</v>
@@ -13755,7 +13755,7 @@
         <v>PASS</v>
       </c>
       <c r="L308" t="str">
-        <v>0.069s</v>
+        <v>0.043s</v>
       </c>
       <c r="M308" t="str">
         <v>N/A</v>
@@ -13798,7 +13798,7 @@
         <v>PASS</v>
       </c>
       <c r="L309" t="str">
-        <v>0.087s</v>
+        <v>0.135s</v>
       </c>
       <c r="M309" t="str">
         <v>N/A</v>
@@ -13841,7 +13841,7 @@
         <v>PASS</v>
       </c>
       <c r="L310" t="str">
-        <v>0.060s</v>
+        <v>0.086s</v>
       </c>
       <c r="M310" t="str">
         <v>N/A</v>
@@ -13884,7 +13884,7 @@
         <v>PASS</v>
       </c>
       <c r="L311" t="str">
-        <v>0.135s</v>
+        <v>0.124s</v>
       </c>
       <c r="M311" t="str">
         <v>N/A</v>
@@ -13927,7 +13927,7 @@
         <v>PASS</v>
       </c>
       <c r="L312" t="str">
-        <v>0.095s</v>
+        <v>0.142s</v>
       </c>
       <c r="M312" t="str">
         <v>N/A</v>
@@ -13970,7 +13970,7 @@
         <v>PASS</v>
       </c>
       <c r="L313" t="str">
-        <v>0.041s</v>
+        <v>0.147s</v>
       </c>
       <c r="M313" t="str">
         <v>N/A</v>
@@ -14013,7 +14013,7 @@
         <v>PASS</v>
       </c>
       <c r="L314" t="str">
-        <v>0.061s</v>
+        <v>0.069s</v>
       </c>
       <c r="M314" t="str">
         <v>N/A</v>
@@ -14056,7 +14056,7 @@
         <v>PASS</v>
       </c>
       <c r="L315" t="str">
-        <v>0.089s</v>
+        <v>0.045s</v>
       </c>
       <c r="M315" t="str">
         <v>N/A</v>
@@ -14099,7 +14099,7 @@
         <v>PASS</v>
       </c>
       <c r="L316" t="str">
-        <v>0.123s</v>
+        <v>0.043s</v>
       </c>
       <c r="M316" t="str">
         <v>N/A</v>
@@ -14142,7 +14142,7 @@
         <v>PASS</v>
       </c>
       <c r="L317" t="str">
-        <v>0.101s</v>
+        <v>0.070s</v>
       </c>
       <c r="M317" t="str">
         <v>N/A</v>
@@ -14185,7 +14185,7 @@
         <v>PASS</v>
       </c>
       <c r="L318" t="str">
-        <v>0.053s</v>
+        <v>0.103s</v>
       </c>
       <c r="M318" t="str">
         <v>N/A</v>
@@ -14228,7 +14228,7 @@
         <v>PASS</v>
       </c>
       <c r="L319" t="str">
-        <v>0.116s</v>
+        <v>0.065s</v>
       </c>
       <c r="M319" t="str">
         <v>N/A</v>
@@ -14271,7 +14271,7 @@
         <v>PASS</v>
       </c>
       <c r="L320" t="str">
-        <v>0.116s</v>
+        <v>0.105s</v>
       </c>
       <c r="M320" t="str">
         <v>N/A</v>
@@ -14314,7 +14314,7 @@
         <v>PASS</v>
       </c>
       <c r="L321" t="str">
-        <v>0.155s</v>
+        <v>0.045s</v>
       </c>
       <c r="M321" t="str">
         <v>N/A</v>
@@ -14357,7 +14357,7 @@
         <v>PASS</v>
       </c>
       <c r="L322" t="str">
-        <v>0.142s</v>
+        <v>0.103s</v>
       </c>
       <c r="M322" t="str">
         <v>N/A</v>
@@ -14400,7 +14400,7 @@
         <v>PASS</v>
       </c>
       <c r="L323" t="str">
-        <v>0.144s</v>
+        <v>0.047s</v>
       </c>
       <c r="M323" t="str">
         <v>N/A</v>
@@ -14443,7 +14443,7 @@
         <v>PASS</v>
       </c>
       <c r="L324" t="str">
-        <v>0.121s</v>
+        <v>0.151s</v>
       </c>
       <c r="M324" t="str">
         <v>N/A</v>
@@ -14486,7 +14486,7 @@
         <v>PASS</v>
       </c>
       <c r="L325" t="str">
-        <v>0.074s</v>
+        <v>0.130s</v>
       </c>
       <c r="M325" t="str">
         <v>N/A</v>
@@ -14529,7 +14529,7 @@
         <v>PASS</v>
       </c>
       <c r="L326" t="str">
-        <v>0.125s</v>
+        <v>0.043s</v>
       </c>
       <c r="M326" t="str">
         <v>N/A</v>
@@ -14572,7 +14572,7 @@
         <v>PASS</v>
       </c>
       <c r="L327" t="str">
-        <v>0.068s</v>
+        <v>0.101s</v>
       </c>
       <c r="M327" t="str">
         <v>N/A</v>
@@ -14615,7 +14615,7 @@
         <v>PASS</v>
       </c>
       <c r="L328" t="str">
-        <v>0.101s</v>
+        <v>0.085s</v>
       </c>
       <c r="M328" t="str">
         <v>N/A</v>
@@ -14658,7 +14658,7 @@
         <v>PASS</v>
       </c>
       <c r="L329" t="str">
-        <v>0.042s</v>
+        <v>0.078s</v>
       </c>
       <c r="M329" t="str">
         <v>N/A</v>
@@ -14701,7 +14701,7 @@
         <v>PASS</v>
       </c>
       <c r="L330" t="str">
-        <v>0.094s</v>
+        <v>0.150s</v>
       </c>
       <c r="M330" t="str">
         <v>N/A</v>
@@ -14744,7 +14744,7 @@
         <v>PASS</v>
       </c>
       <c r="L331" t="str">
-        <v>0.042s</v>
+        <v>0.138s</v>
       </c>
       <c r="M331" t="str">
         <v>N/A</v>
@@ -14787,7 +14787,7 @@
         <v>PASS</v>
       </c>
       <c r="L332" t="str">
-        <v>0.090s</v>
+        <v>0.134s</v>
       </c>
       <c r="M332" t="str">
         <v>N/A</v>
@@ -14830,7 +14830,7 @@
         <v>PASS</v>
       </c>
       <c r="L333" t="str">
-        <v>0.123s</v>
+        <v>0.144s</v>
       </c>
       <c r="M333" t="str">
         <v>N/A</v>
@@ -14873,7 +14873,7 @@
         <v>PASS</v>
       </c>
       <c r="L334" t="str">
-        <v>0.114s</v>
+        <v>0.131s</v>
       </c>
       <c r="M334" t="str">
         <v>N/A</v>
@@ -14916,7 +14916,7 @@
         <v>PASS</v>
       </c>
       <c r="L335" t="str">
-        <v>0.043s</v>
+        <v>0.051s</v>
       </c>
       <c r="M335" t="str">
         <v>N/A</v>
@@ -14959,7 +14959,7 @@
         <v>PASS</v>
       </c>
       <c r="L336" t="str">
-        <v>0.141s</v>
+        <v>0.071s</v>
       </c>
       <c r="M336" t="str">
         <v>N/A</v>
@@ -15002,7 +15002,7 @@
         <v>PASS</v>
       </c>
       <c r="L337" t="str">
-        <v>0.075s</v>
+        <v>0.069s</v>
       </c>
       <c r="M337" t="str">
         <v>N/A</v>
@@ -15045,7 +15045,7 @@
         <v>PASS</v>
       </c>
       <c r="L338" t="str">
-        <v>0.054s</v>
+        <v>0.121s</v>
       </c>
       <c r="M338" t="str">
         <v>N/A</v>
@@ -15088,7 +15088,7 @@
         <v>PASS</v>
       </c>
       <c r="L339" t="str">
-        <v>0.157s</v>
+        <v>0.136s</v>
       </c>
       <c r="M339" t="str">
         <v>N/A</v>
@@ -15131,7 +15131,7 @@
         <v>PASS</v>
       </c>
       <c r="L340" t="str">
-        <v>0.138s</v>
+        <v>0.146s</v>
       </c>
       <c r="M340" t="str">
         <v>N/A</v>
@@ -15174,7 +15174,7 @@
         <v>PASS</v>
       </c>
       <c r="L341" t="str">
-        <v>0.090s</v>
+        <v>0.061s</v>
       </c>
       <c r="M341" t="str">
         <v>N/A</v>
@@ -15217,7 +15217,7 @@
         <v>PASS</v>
       </c>
       <c r="L342" t="str">
-        <v>0.082s</v>
+        <v>0.041s</v>
       </c>
       <c r="M342" t="str">
         <v>N/A</v>
@@ -15260,7 +15260,7 @@
         <v>PASS</v>
       </c>
       <c r="L343" t="str">
-        <v>0.133s</v>
+        <v>0.063s</v>
       </c>
       <c r="M343" t="str">
         <v>N/A</v>
@@ -15303,7 +15303,7 @@
         <v>PASS</v>
       </c>
       <c r="L344" t="str">
-        <v>0.047s</v>
+        <v>0.085s</v>
       </c>
       <c r="M344" t="str">
         <v>N/A</v>
@@ -15346,7 +15346,7 @@
         <v>PASS</v>
       </c>
       <c r="L345" t="str">
-        <v>0.077s</v>
+        <v>0.102s</v>
       </c>
       <c r="M345" t="str">
         <v>N/A</v>
@@ -15389,7 +15389,7 @@
         <v>PASS</v>
       </c>
       <c r="L346" t="str">
-        <v>0.095s</v>
+        <v>0.066s</v>
       </c>
       <c r="M346" t="str">
         <v>N/A</v>
@@ -15432,7 +15432,7 @@
         <v>PASS</v>
       </c>
       <c r="L347" t="str">
-        <v>0.047s</v>
+        <v>0.082s</v>
       </c>
       <c r="M347" t="str">
         <v>N/A</v>
@@ -15475,7 +15475,7 @@
         <v>PASS</v>
       </c>
       <c r="L348" t="str">
-        <v>0.073s</v>
+        <v>0.072s</v>
       </c>
       <c r="M348" t="str">
         <v>N/A</v>
@@ -15518,7 +15518,7 @@
         <v>PASS</v>
       </c>
       <c r="L349" t="str">
-        <v>0.156s</v>
+        <v>0.066s</v>
       </c>
       <c r="M349" t="str">
         <v>N/A</v>
@@ -15561,7 +15561,7 @@
         <v>PASS</v>
       </c>
       <c r="L350" t="str">
-        <v>0.144s</v>
+        <v>0.096s</v>
       </c>
       <c r="M350" t="str">
         <v>N/A</v>
@@ -15604,7 +15604,7 @@
         <v>PASS</v>
       </c>
       <c r="L351" t="str">
-        <v>0.041s</v>
+        <v>0.114s</v>
       </c>
       <c r="M351" t="str">
         <v>N/A</v>
@@ -15647,7 +15647,7 @@
         <v>PASS</v>
       </c>
       <c r="L352" t="str">
-        <v>0.090s</v>
+        <v>0.084s</v>
       </c>
       <c r="M352" t="str">
         <v>N/A</v>
@@ -15690,7 +15690,7 @@
         <v>PASS</v>
       </c>
       <c r="L353" t="str">
-        <v>0.106s</v>
+        <v>0.103s</v>
       </c>
       <c r="M353" t="str">
         <v>N/A</v>
@@ -15733,7 +15733,7 @@
         <v>PASS</v>
       </c>
       <c r="L354" t="str">
-        <v>0.087s</v>
+        <v>0.097s</v>
       </c>
       <c r="M354" t="str">
         <v>N/A</v>
@@ -15776,7 +15776,7 @@
         <v>PASS</v>
       </c>
       <c r="L355" t="str">
-        <v>0.115s</v>
+        <v>0.143s</v>
       </c>
       <c r="M355" t="str">
         <v>N/A</v>
@@ -15819,7 +15819,7 @@
         <v>PASS</v>
       </c>
       <c r="L356" t="str">
-        <v>0.112s</v>
+        <v>0.157s</v>
       </c>
       <c r="M356" t="str">
         <v>N/A</v>
